--- a/_webui-downloaded.xlsx
+++ b/_webui-downloaded.xlsx
@@ -66,7 +66,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/9/22 17:28:48</t>
+          <t xml:space="preserve">2026/9/22 17:35:03</t>
         </is>
       </c>
     </row>
